--- a/data/Additionalinsuredcomps.xlsx
+++ b/data/Additionalinsuredcomps.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C172"/>
+  <dimension ref="A1:B146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">PARTNERS </t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>EMAIL ADDRESS</t>
+          <t>PARTNERS</t>
         </is>
       </c>
     </row>
@@ -457,11 +452,6 @@
 KNOXVILLE, TN 37919</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>jane@expediteall.com /  hr.department@expediteall.com</t>
-        </is>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -471,13 +461,8 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>61 Bradshaw Lane, 
+          <t>61 Bradshaw Lane,
 Candler, NC 28715</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> hr.department@rppexpress.com /safety.expedite@rppexpress.com</t>
         </is>
       </c>
     </row>
@@ -490,12 +475,7 @@
       <c r="B4" t="inlineStr">
         <is>
           <t>603 Canterbury Rd,
-Kings Mountain, NC  28086</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>hrexpedite@deltaexpressinc.com/  safety.team@deltaexpressinc.com</t>
+Kings Mountain, NC 28086</t>
         </is>
       </c>
     </row>
@@ -511,11 +491,6 @@
 Chagrin Falls, OH 44023</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hr.department@landseatransportationinc.co </t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,11 +504,6 @@
 Indianapolis, IN 46235</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hr.department@exclusivetransportationinc.com</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -547,11 +517,6 @@
 Aston, PA 19014</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>hr-department@greenlinepa.com</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -565,16 +530,11 @@
 Aston, PA 19014</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>hr.exp@freightallianceinc.com</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">National Freight Lines INC </t>
+          <t>National Freight Lines INC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -583,16 +543,11 @@
 Asheboro NC 27203</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hrs@nationalfli.com</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">Continental Logistics INC  </t>
+          <t>Continental Logistics INC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -601,81 +556,55 @@
 Asheboro NC 27203</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>hr.exp@continentalloginc.com</t>
-        </is>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carolina transportation INC </t>
+          <t>Carolina transportation INC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>120 Dogwood Rd, 
+          <t>120 Dogwood Rd,
 Candler, NC 28715</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>hr@carolinatransportationinc.com</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premium Logistics INC </t>
+          <t>Premium Logistics INC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>6000 Fairview Rd Ste 1271 
+          <t>6000 Fairview Rd Ste 1271
 Charlotte, NС 28210</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>hrdepartment@premiumlogisticsinc.com</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highway Express INC </t>
+          <t>Highway Express INC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800 E Blue Lick Rd Suite 7 Shepherdsville, KY 40165
-</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>hr.expedite@highwayexpressinc.com</t>
+          <t>1800 E Blue Lick Rd Suite 7 Shepherdsville, KY 40165</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Advantage Logistics INC </t>
+          <t>Advantage Logistics INC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>116 White Oak Lane, Suite J 
+          <t>116 White Oak Lane, Suite J
 Lexington, SC 29073</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hrdepartment@advantage-logisticsinc.com</t>
         </is>
       </c>
     </row>
@@ -687,13 +616,8 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>3439 SE Hawthorne Blvd #1015 
+          <t>3439 SE Hawthorne Blvd #1015
 Portland, OR 97214</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hrexpedite@greenwayexpressllc.com</t>
         </is>
       </c>
     </row>
@@ -709,11 +633,6 @@
 Greenville, SC, 29605</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>hr.exp@soundtransportationinc.com</t>
-        </is>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -723,13 +642,8 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16261 Hollister Street, Suite A-85, 
+          <t>16261 Hollister Street, Suite A-85,
 Houston, TX 77066</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>hrdepartment@alliancecargoinc.com</t>
         </is>
       </c>
     </row>
@@ -741,13 +655,8 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1942 West Morris Blvd 
+          <t>1942 West Morris Blvd
 Morristown, TN 37814</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>hrdepartment@selectlogisticsinc.com</t>
         </is>
       </c>
     </row>
@@ -759,31 +668,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>626 HARPER AVENUE SUITE 7 
+          <t>626 HARPER AVENUE SUITE 7
 LENOIR, NC 28645</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>hr.expedited@allyenterprisesllc.com</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">Superior Transportation Inc </t>
+          <t>Superior Transportation Inc</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>6220 Hudspeth Rd, 
+          <t>6220 Hudspeth Rd,
 Harrisburg, NC 28075</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>hr.expedited@superiortransportationinc.com</t>
         </is>
       </c>
     </row>
@@ -795,13 +694,8 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>11918 SE Division St 183 
+          <t>11918 SE Division St 183
 Portland OR 97266</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>hr.expedited@eexp.com</t>
         </is>
       </c>
     </row>
@@ -813,13 +707,8 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">3556 S 5600 W 1 636 
-WEST VALLEY CITY, UT 84104 </t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hr.expedited@allstatesexpressinc.com</t>
+          <t>3556 S 5600 W 1 636
+WEST VALLEY CITY, UT 84104</t>
         </is>
       </c>
     </row>
@@ -831,2416 +720,1595 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>6608 N western Ave #1472 
+          <t>6608 N western Ave #1472
 Oklahoma City, OK 73116</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>hrdepartment@primetimefreightinc.com</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">Highway Express INC </t>
+          <t>Rainier Transportation INC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1151 FALLS RD BUILDING D STE 1030
-ROCKY MOUNT, NC 27804</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>3702 N West Valley Hwy, Suite 210
+Auburn, WA 98001</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rainier Transportation INC
-</t>
+          <t>Delta Logistics INC</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>3702 N West Valley Hwy, Suite 210
-Auburn, WA 98001</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>hr.expedite@rainiertransportation.com</t>
+          <t>10502 St. Joseph Drive
+Dubuque, IA 52003</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Delta Logistics INC</t>
+          <t>Link Logistics Inc</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>10502 St. Joseph Drive 
-Dubuque, IA 52003</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>hr.expedite@deltalogisticsinc.com
-amira@deltalogisticsinc.com</t>
+          <t>1140 Monticello Rd Ste 180D
+Madison, GA 30650</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Link Logistics Inc
-</t>
+          <t>Pacific Transportation INC</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1140 Monticello Rd Ste 180D
-Madison, GA 30650</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>allhr@link-logisticsinc.com</t>
+          <t>2300 S ORCHARD ST STE F
+BOISE, ID 83705</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pacific Transportation INC </t>
+          <t>ATLANTIC CARGO INC</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2300 S ORCHARD ST STE F 
-BOISE, ID 83705</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>nick@pacifictransportationinc.com</t>
+          <t>1033 3RD AVE STE 215
+CARMEL, IN 46032</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ATLANTIC CARGO INC</t>
+          <t>Carolina Logistics Inc</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1033 3RD AVE STE 215 
-CARMEL, IN 46032</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>yana@atlanticcargoinc.com</t>
+          <t>4450 Parris Bridge Rd
+Boiling Springs, SC 29316</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Carolina Logistics Inc</t>
+          <t>AmbuFreight INC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>4450 Parris Bridge Rd 
-Boiling Springs, SC 29316</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>hr.department@carolinalogisticsinc.com</t>
+          <t>4800 W 34TH STREET STE C51,
+HOUSTON, TX 77092</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ONTRACK TRANSPORTATION INC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1151 FALLS ROAD, BLDG. D, STE. 1030
+ROCKY MOUNT, NC 27804</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AmbuFreight INC</t>
+          <t>PIONEER LOGISTICS INC.</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>4800 W 34TH STREET STE C51,
-HOUSTON, TX 77092</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>ambuhr@ambufreight.com  
-lisa@ambufreight.com</t>
+          <t>2300 WILSON BLVD SUITE 700 #1088
+ARLINGTON, VA 22201</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Precise Transportation Inc</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>46 Haywood St Ste 360
+Asheville, NC 28801</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ONTRACK TRANSPORTATION INC</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>1151 FALLS ROAD, BLDG. D, STE. 1030 
-ROCKY MOUNT, NC 27804</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>hr.ontrack@ontracktransportationinc.com</t>
-        </is>
-      </c>
+          <t>OTHERS</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>iTake Express LLC</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>5485 Bethelview RD, Ste 360-317,
+Cumming, GA 30040</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PIONEER LOGISTICS INC.</t>
+          <t>CONNEX TRANSPORT LLC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2300 WILSON BLVD SUITE 700 #1088 
-ARLINGTON, VA 22201</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>safety.exp@pioneerlogisticsinc.com</t>
+          <t>2885 KIETZKE LN STE 2
+RENO, NV 89502</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Precise Transportation Inc
-</t>
+          <t>FAIRMOUNT GLOBAL FREIGHT LLC</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>46 Haywood St Ste 360
-Asheville, NC 28801</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hrteam@precisetransportationinc.com
-</t>
+          <t>630 NORTH 22 ND ST
+Philadelphia, PA 19130</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Empire National Inc</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OTHER</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>5045 Hendersonville Rd Unit 1
+Fletcher, NC 28732</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>OTHERS</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
+          <t>Empire Expedited Inc</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1620 Asheville Hwy, Suite 207
+Hendersonville, NC 28791</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>iTake Express LLC</t>
+          <t>Hippix Logistix</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5485 Bethelview RD, Ste 360-317,
-Cumming, GA 30040</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>HR@itakexpress.com</t>
+          <t>PO BOX 21715
+Chattanooga, TN 37424</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CONNEX TRANSPORT LLC</t>
+          <t>MILLHOUSE LOGISTICS SERVICES LLC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2885 KIETZKE LN STE 2
-RENO, NV 89502</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>richardhr@shipconnex.com</t>
+          <t>145 Cane Creek Industrial Park Road, Suite #150Fletcher, NC 28732</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>FAIRMOUNT GLOBAL FREIGHT LLC</t>
+          <t>BRONPE LLC</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>630 NORTH 22 ND ST
-Philadelphia , PA 19130</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ad@fairmountgf.com
-kwhite@fairmountgf.com</t>
+          <t>481 METROPOLITAN ST,
+AURORA, IL 60502</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Empire National Inc</t>
+          <t>OVN LLC</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>5045 Hendersonville Rd Unit 1
-Fletcher, NC 28732</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t xml:space="preserve">carryed@empirenational.com  / ianma@empirenational.com / kurtbu@empirenational.com  </t>
+          <t>188 Seegers Ave
+Elk Grove Village, IL 60007</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Empire Expedited Inc</t>
+          <t>Hugo Hunter INC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1620 Asheville Hwy, Suite 207
-Hendersonville, NC 28791</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>ronaldha@empirenational.com</t>
+          <t>4250 Trailer Drive
+Charlotte, NC 28269</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Hippix Logistix</t>
+          <t>Hugo Hunter Express INC</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PO BOX 21715
-Chattanooga, TN 37424</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>giana@hippixlogistix.com</t>
+          <t>313 Trindale Rd Ste 201
+Archdale, NC 27263</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MILLHOUSE LOGISTICS SERVICES LLC</t>
+          <t>Zubr Freight LLC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">145 Cane Creek Industrial Park Road, Suite #150Fletcher, NC 28732  
-</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>safety@millhouse.com</t>
+          <t>216 Lockart Ter, 1st fl,
+Philadelphia PA 19116</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BRONPE LLC</t>
+          <t>Odysseia Inc</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>481 METROPOLITAN ST, 
-AURORA, IL 60502</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>hr@bronpe.com</t>
+          <t>521 S Port St.
+Baltimore, MD 21224</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>OVN LLC</t>
+          <t>STARLINE EXPEDITE LLC</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>188 Seegers Ave 
-Elk Grove Village, IL 60007</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>hr@ovn.llc</t>
+          <t>70 Birch Alley Ste 240
+Beavercreek, OH 45440</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Hugo Hunter INC</t>
+          <t>Alpha Express LLC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>4250 Trailer Drive  
-Charlotte, NC 28269</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>hrexpedite@hugohunter.com</t>
+          <t>927 Thunder Gulch Drive
+Boiling Springs SC 29316</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Hugo Hunter Express INC</t>
+          <t>One Transport LLC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>313 Trindale Rd Ste 201
-Archdale, NC 27263</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>hrexpedite@hugohunter.com</t>
+          <t>6725 S Fry Rd
+Katy, TX 77494</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve"> Zubr Freight LLC</t>
+          <t>USKO EXPEDITE INC</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>216 Lockart Ter, 1st fl, 
-Philadelphia PA 19116</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>lera@zubrllc.com</t>
+          <t>1101 Creekside Ridge Dr Suite 270,
+Roseville, CA 95678</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Odysseia Inc</t>
+          <t>GTMM Transportation LLC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>521 S Port St. 
-Baltimore, MD 21224</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Julia@odysseia.one
-hr@odysseia.one</t>
+          <t>816 Pine Ridge St.
+Sanford, NC 27330</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">STARLINE EXPEDITE LLC </t>
+          <t>UT Services inc</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>70 Birch Alley Ste 240 
-Beavercreek, OH 45440</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>801 Brickell Ave Suite 800
+Miami FL 33131</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Carolina Logistics Inc</t>
+          <t>X- Path Trucking LLC</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>4450 Parris Bridge Rd 
-Boiling Springs, SC 29316</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>salah@carolinalogisticsinc.com</t>
+          <t>10146 Hartford CenterApt 3B
+Schiller Park, IL 60176</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Homeland Transport INC</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>1151 Mchenry Rd Ste 205A
+Buffalo Grove, IL 60089</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AmbuFreight INC</t>
+          <t>Acies Transport LLC</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>4800 W 34TH STREET STE C51,
-HOUSTON, TX 77092</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>lisa@ambufreight.com</t>
+          <t>12375 Kinsman Rd Building H STE 12
+Newbury Township, OH 44065</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
-      <c r="C57" t="inlineStr"/>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>HUBSN INC</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>291 CAMBRIDGE LN
+NEWTOWN, PA 18940</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Alpha Express LLC</t>
+          <t>Victoria Logistics Carrier LLC</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>927 Thunder Gulch Drive
-Boiling Springs SC 29316</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>hr@aexpressllc.com</t>
+          <t>5710 6TH AVE APT 212
+ST PETERSBURG, FL 33710</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
-      <c r="C59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>EML TRANSPORTATION INC</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>5278 MIDDLE CTS                                     ORLANDO, FL 32811</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>One Transport LLC</t>
+          <t>2131 TRANSPORTATION LLC</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>6725 S Fry Rd  
-Katy, TX 77494</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">	ap@wtload.com</t>
+          <t>625 SAWYER DR
+SAGINAW, TX 76179</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>USKO EXPEDITE INC</t>
+          <t>UNITED FLEET CORP</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1101 Creekside Ridge Dr Suite 270, 
-Roseville, CA 95678</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>recruiting@uskoexpedite.com</t>
+          <t>700 Remington Rd Suite E
+Schaumburg, IL 60173</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
-      <c r="C62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>VECTOR FLEET CORP</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>3 GRANT SQ UNIT 121                                          HINSDALE, IL 60521</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GTMM Transportation LLC</t>
+          <t>WESTERN TRUCKING INC</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>816 Pine Ridge St.
-Sanford, NC 27330</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t xml:space="preserve">hr@gtmmtransportation.com
-</t>
+          <t>PO BOX 1277
+WEST SPRINGFIELD, MA 01090</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
-      <c r="C64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>ANN LOGISTICS LLC</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>5517 IVYRIDGE LN
+MCKINNEY, TX 75071</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>UT Services inc</t>
+          <t>S'ONE EXPRESS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>801 Brickell Ave Suite 800
-Miami FL 33131</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>sara@utscor.com  william@utscor.com vlad@utscor.com</t>
+          <t>5160 MAY AVE                                                    FAIRFIELD, OH 45014</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>X- Path Trucking LLC</t>
+          <t>SMART PROVIDE LLC</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10146 Hartford CenterApt 3B
-Schiller Park, IL 60176</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>driver@xpathtrucking.com</t>
+          <t>1701 1ST AVE S
+SEATTLE, WA 98134</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Homeland Transport INC</t>
+          <t>Safe Capital Group</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1151 Mchenry Rd Ste 205A
-Buffalo Grove, IL 60089</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>hrexpedite@homelandtransportinc.com</t>
+          <t>777 NE 7th Street 205
+Grants Pass, OR 97526</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Acies Transport LLC</t>
+          <t>Fox Carriers</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>12375 Kinsman Rd Building H STE 12 
-Newbury Township, OH 44065</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>mary@aciestransport.com / aciesllcusa@gmail.com</t>
+          <t>2512 E Evergreen Blvd PMB 3027
+Vancouver, WA 98661</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">HUBSN INC </t>
+          <t>Zajecar LLC</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>291 CAMBRIDGE LN 
-NEWTOWN, PA 18940</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>job@hubsn.com</t>
+          <t>7459 N Waukegan Rd
+Niles, IL 60714</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Victoria Logistics Carrier LLC</t>
+          <t>Metro Trans Logistics LLC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">5710 6TH AVE APT 212  
-ST PETERSBURG, FL 33710
-</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">trucking@vlcdisp.com  hr2@vlcdisp.com
-</t>
+          <t>41 Ethan Drive #1A
+New Providence NJ 07974</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>EML TRANSPORTATION INC</t>
+          <t>Gaga Transportation Inc</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>5278 MIDDLE CTS                                     ORLANDO, FL 32811</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>6201 BAY PKWY APT D8
+Brooklyn, NY 11204</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2131 TRANSPORTATION LLC</t>
+          <t>Tradex Logistics Inc.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>625 SAWYER DR
-SAGINAW, TX 76179</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Kamilajohnson@2131trucking.com
-dispatch@2131trucking.com</t>
+          <t>607 Grand Central Blvd,
+Laredo, TX 78045</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>UNITED FLEET CORP</t>
+          <t>OFFMAX Logistics LLC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>700 Remington Rd Suite E             
-Schaumburg, IL 60173</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>hr@ufleetcorp.com / thomas@ufleetcorp.com</t>
+          <t>1801 N Greenville Ave 3127
+Richardson, TX 75081</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>VECTOR FLEET CORP</t>
+          <t>Xpath Trucking LLC</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>3 GRANT SQ UNIT 121                                          HINSDALE, IL 60521</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
+          <t>10146 Hartford court, apt 3B
+Schiller Park, IL 60176</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>WESTERN TRUCKING INC</t>
+          <t>ROCKET SECURE CARGO LLC</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>PO BOX 1277
-WEST SPRINGFIELD, MA 01090</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>doc@wtload.com</t>
+          <t>205 Minerales Annex Rd
+Laredo, TX 78045</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ANN LOGISTICS LLC</t>
+          <t>BY EXPRESS LLC</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>5517 IVYRIDGE LN
-MCKINNEY, TX 75071</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>hr@annlogistics.com</t>
+          <t>20321 Alger St
+Saint Clair Shores, MI 48080</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">S'ONE EXPRESS </t>
+          <t>Unique For Logistics LLC</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>5160 MAY AVE                                                    FAIRFIELD, OH 45014</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>102 E Pennsylvania Blvd
+Feasterville-Trevose, PA 19053</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SMART PROVIDE LLC</t>
+          <t>FORCE TRANS INC</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1701 1ST AVE S  
-SEATTLE, WA 98134</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>hr@sprovide.info</t>
+          <t>4700 ROSEVILLE RD SUITE-102
+NORTH HIGHLANDS, CA 95660</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">Safe Capital Group
-</t>
+          <t>URSA EXPRESS Transportation LLC</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>777 NE 7th Street 205
-Grants Pass, OR 97526</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>hr@safecapg.com</t>
+          <t>1427 KATHLEEN CT
+JAMISON, PA 18929</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Fox Carriers</t>
+          <t>MMM Express</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2512 E Evergreen Blvd PMB 3027
-Vancouver, WA 98661</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>eren@foxcarriers.com</t>
+          <t>796 Bill Rutledge Road
+WINDER, GA 30680</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Zajecar LLC
-</t>
+          <t>MT TRANS EXPRESS INC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>7459 N Waukegan Rd 
-Niles, IL 60714</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
+          <t>1143 SURREY RD
+PHILADELPHIA, PA 19115</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Metro Trans Logistics LLC
-</t>
+          <t>CNU Logistics</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>41 Ethan Drive #1A
-New Providence NJ 07974</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Recruiting@mtlfreight.com</t>
+          <t>1795 STOUT DR
+WARMINSTER, PA 18974</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gaga Transportation Inc </t>
+          <t>Direct Express LLC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>6201 BAY PKWY APT D8
-Brooklyn, NY 11204</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>recruiter@gaga-transportation.com
-eva@gaga-transportation.com
-hr@gaga-transportation.com</t>
+          <t>236 E Main St #275
+SEVIERVILLE, TN 37862</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Tradex Logistics Inc.</t>
+          <t>Double Leap LLC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>607 Grand Central Blvd,
-Laredo, TX 78045</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Tradex International LLC</t>
+          <t>11728 WULSTONE RD
+HASLET, TX 76052</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>OFFMAX Logistics LLC</t>
+          <t>Instant Worldwide Shipping LLC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1801 N Greenville Ave 3127
-Richardson, TX 75081</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
+          <t>18062 FM 529 RD STE 182
+CYPRESS, TX 77433</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Xpath Trucking LLC</t>
+          <t>Turbo XPD LLC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10146 Hartford court, apt 3B
-Schiller Park, IL 60176</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>4300 Business Park Ct
+Lilburn, GA 30047</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ROCKET SECURE CARGO LLC</t>
+          <t>NDAMBIRI RENTAL LLC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>205 Minerales Annex Rd 
-Laredo, TX 78045</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>hr@exp.rocketsecurecargo.com</t>
+          <t>1823 RUSTICA DRIVE
+DURHAM, NC 27713</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">BY EXPRESS LLC </t>
+          <t>Oliver Group Inc</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>20321 Alger St
-Saint Clair Shores, MI 48080</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>hr@byexpressllc.com</t>
+          <t>1427 Kathleen Ct
+Jamison PA, 18929</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Unique For Logistics LLC</t>
+          <t>VERTEX TRANSPORTATION LLC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>102 E Pennsylvania Blvd
-Feasterville-Trevose, PA 19053</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>job@uniforlogy.com</t>
+          <t>4299 Hawk Cir,
+Doylestown, PA 18902</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>FORCE TRANS INC</t>
+          <t>Premier Logistics LLC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t xml:space="preserve">4700 ROSEVILLE RD SUITE-102
-NORTH HIGHLANDS, CA   95660  </t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>info@force-trans.com</t>
+          <t>1666 Morrow St,
+Green Bay, WI 54302</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>URSA EXPRESS Transportation LLC</t>
+          <t>RP EXPEDITING LLC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1427 KATHLEEN CT
-JAMISON, PA 18929</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Jen@ursaexpress.com</t>
+          <t>632 INGLESBY PKWY
+DUNCAN, SC 29334</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>MMM Express</t>
+          <t>Alliance Logistics LLC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>796 Bill Rutledge Road
-WINDER, GA 30680</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>xpd@mmm-express.com</t>
+          <t>305 Olive Ave B,
+Horsham, PA 19044,</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">MT TRANS EXPRESS INC
-</t>
+          <t>AGAMIR</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t xml:space="preserve"> 1143 SURREY RD 
-PHILADELPHIA, PA 19115</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
+          <t>331 PACKANACK DR                                                                   GOULDSBORO, PA 18424</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CNU Logistics</t>
+          <t>NATIONAL CAPITAL LOGISTICS LLC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1795 STOUT DR
-WARMINSTER, PA 18974</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>anya@cnulogistics.com</t>
+          <t>2601 Jackson Ave #1221                                                                   Ann Arbor, MI 48103</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Direct Express LLC</t>
+          <t>Logistics Systems LLC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>236 E Main St #275
-SEVIERVILLE, TN 37862</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>hr@directexpressllc.com</t>
+          <t>207 BUCK RD, SUITE 3
+SOUTHAMPTON, PA 18966</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Double Leap LLC</t>
+          <t>ENK LOGISTIC GROUP</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>11728 WULSTONE RD 
-HASLET, TX 76052</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr"/>
+          <t>4134 COVE LN UNIT F                                GLENVIEW, IL 60025</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Instant Worldwide Shipping LLC</t>
+          <t>US-SERVICE INC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>18062 FM 529 RD STE 182 
-CYPRESS, TX 77433</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>hr@iwscarriers.com</t>
+          <t>2222 PONCE DE LEON BLVD 3RD FLOOR                                MIAMI, FL 33134</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Turbo XPD LLC</t>
+          <t>Creekside Cargo</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>4300 Business Park Ct
-Lilburn, GA 30047</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>15416 Industrial Pkwy                                                         Cleveland, OH 44135</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>NDAMBIRI RENTAL LLC</t>
+          <t>HIPTIX LOGISTIX</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1823 RUSTICA DRIVE 
-DURHAM, NC 27713</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>PO BOX 21715
+CHATTANOOGA, TN 37424</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Oliver Group Inc</t>
+          <t>Nitro Logistics Inc</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1427 Kathleen Ct 
-Jamison PA, 18929</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Dispatch@olivergroupincorp.com</t>
+          <t>23414 Woodlawn Ridge.
+San Antonio, TX 78259</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">VERTEX TRANSPORTATION LLC
-</t>
+          <t>First Tranz LLC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>4299 Hawk Cir,
-Doylestown, PA 18902</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr"/>
+          <t>101 North Tryon Street Suite 112
+Charlotte, NC 28246</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Premier Logistics LLC
-</t>
+          <t>Windy Expedite Inc</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1666 Morrow St,
-Green Bay, WI 54302</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr"/>
+          <t>1405 Bernard Dr, Ste, D.
+Addison, IL 60101</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">RP EXPEDITING LLC
-</t>
+          <t>4U Logistics LLC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>632 INGLESBY PKWY   
-DUNCAN, SC 29334</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>acct@rpexpediting.com</t>
+          <t>9235 SW 8TH ST, APT 214
+BOCA RATON, FL 33428</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alliance Logistics LLC
-</t>
+          <t>VIP Expedited</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>305 Olive Ave B,
-Horsham, PA 19044,</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>2906 Winding Trail Dr.
+Valrico, FL 33596</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">AGAMIR  </t>
+          <t>MANAMIS INC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>331 PACKANACK DR                                                                   GOULDSBORO, PA 18424</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr"/>
+          <t>700 SOUTH CENTRAK EXPRESSWAY
+ALLEN TX 75013</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>NATIONAL CAPITAL LOGISTICS LLC</t>
+          <t>Bravo Express INC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2601 Jackson Ave #1221                                                                   Ann Arbor, MI 48103</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr"/>
+          <t>1111 TINKER RD UNIT 1
+ROCKLIN, CA 95765</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Logistics Systems LLC
-</t>
+          <t>ZS Cargo LLC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>207 BUCK RD, SUITE 3
-SOUTHAMPTON, PA 18966</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>ray@logisticssystemsllc.com</t>
+          <t>1606 Turnbull Dr
+Round Lake Beach, IL 60073</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">ENK LOGISTIC GROUP </t>
+          <t>IRVANOLDHAM LOGISTICS LLC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>4134 COVE LN UNIT F                                GLENVIEW, IL 60025</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr"/>
+          <t>1859 WHITNEY MESA DR, SUITE 2
+HANDERSON, NV 89014</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>US-SERVICE INC</t>
+          <t>Demix Transport Inc</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2222 PONCE DE LEON BLVD 3RD FLOOR                                MIAMI, FL 33134</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>288 Pembridge Ln Unit B1
+Schaumburg, IL 60193</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Creekside Cargo</t>
+          <t>Pennsylvania Logistics LLC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>15416 Industrial Pkwy                                                         Cleveland, OH 44135</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>1631 Loretta Ave Suite D
+Feasterville-Trevose, PA 19053</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">HIPTIX LOGISTIX
-</t>
+          <t>Martlet Inc</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PO BOX 21715
-CHATTANOOGA, TN 37424</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr"/>
+          <t>601 N KENWOOD AVE STE A
+BALTIMORE, MD 21205</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nitro Logistics Inc
-</t>
+          <t>SIGMA EXPRESS LLC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>23414 Woodlawn Ridge.
-San Antonio, TX 78259</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>hr@nitrologistics.us</t>
+          <t>2651 LAKE RIDGE DR2651
+LITTLE ELM, TX 75068</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">First Tranz LLC
-</t>
+          <t>TIGER TRANS GROUP LLC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>101 North Tryon Street Suite 112
-Charlotte, NC 28246</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr"/>
+          <t>47 MCALPIN AVE APT 5
+MAHOPAC NY 10541</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Windy Expedite Inc        </t>
+          <t>Sprinterstate LLC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>1405 Bernard Dr, Ste, D.
-Addison, IL 60101</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr"/>
+          <t>1004 Stevens Pride Ct
+Indian Trail, NC 28079</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>4U Logistics LLC</t>
+          <t>Broad Miles Inc</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>9235 SW 8TH ST, APT 214
-BOCA RATON, FL 33428</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>hr@4u-logistics.com</t>
+          <t>5121 N East River Rd Unit 2H
+Chicago IL 60656</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">VIP Expedited 
-</t>
+          <t>TRANZ AMERICA LLC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2906 Winding Trail Dr.
-Valrico, FL 33596</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>4319 Chuck Hollow Ln, Apt #206
+Charlotte NC 28277</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MANAMIS INC</t>
+          <t>GLOVBE GROUP INC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>700 SOUTH CENTRAK EXPRESSWAY 
-SUTE 400 OFFICE 69
-ALLEN TX 75013</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Anastasia@manamisinc.com</t>
+          <t>9235 Trade Place Unit F
+San Diego, CA 92126</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Bravo Express INC</t>
+          <t>MK TRANSPORTATION INC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>1111 TINKER RD UNIT 1
-ROCKLIN, CA 95765</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>hr@bravofast.com</t>
+          <t>1825 Bridgetown Pike Apt 510
+Feasterville-Trevose 19053</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ZS Cargo LLC</t>
+          <t>ABILOO LLC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>1606 Turnbull Dr
-Round Lake Beach, IL 60073</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr"/>
+          <t>96 BOLTON ST
+MARLBOROUGH, MA 01752</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>IRVANOLDHAM LOGISTICS LLC</t>
+          <t>AVE-TRANS LLC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>1859 WHITNEY MESA DR, SUITE 2 
-HANDERSON, NV 89014</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>hr@iohdispatch.com</t>
+          <t>6800 BERMUDA AVE
+MCKINNEY, TX 75070</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">One Transport LLC </t>
+          <t>Sunnyland Express Corp</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>6725 S Fry Rd
-Katy, TX 77494</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>hr@onetransport.us</t>
+          <t>1336 Oleri Ter
+Fort Lee, NJ 07024</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Demix Transport Inc
-</t>
+          <t>V&amp;T Express</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>288 Pembridge Ln Unit B1
-Schaumburg, IL 60193</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>hr@demixtransport.com</t>
+          <t>113 Ashland Ter
+Boiling Springs, SC 29316</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Pennsylvania Logistics LLC</t>
+          <t>LANA EXPRESS LOGISTICS LLC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>1631 Loretta Ave Suite D
-Feasterville-Trevose, PA 19053</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr"/>
+          <t>2807 ALLEN ST 2067
+DALLAS, TX 75204</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martlet Inc
-</t>
+          <t>Green Oaks Transportation LLC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t xml:space="preserve">601 N KENWOOD AVE STE A
-BALTIMORE, MD  21205 </t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>hr@martlet-express.com</t>
+          <t>27425 Ferry Rd
+Warrenville, IL 60555</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>SIGMA EXPRESS LLC</t>
+          <t>Park Trans LLC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>2651 LAKE RIDGE DR2651
-LITTLE ELM, TX   75068</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>recruit@sigmaexpressllc.com</t>
+          <t>711 Dolly Parton pkwy 4668
+Sevierville, TN 37862</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>TIGER TRANS GROUP LLC</t>
+          <t>DLH TRANS LLC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>47 MCALPIN AVE APT 5
-MAHOPAC NY 10541</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>tigertrans206@gmail.com</t>
+          <t>292 S PINE ST
+SPARTANBURG, SC 29302</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Sprinterstate LLC</t>
+          <t>USA 1 TRUCKING LLC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>1004 Stevens Pride Ct
-Indian Trail, NC 28079</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>hr@sprinterstatellc.com</t>
+          <t>5906 PARK AVE
+CLEVELEND, OH 44105</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Broad Miles Inc</t>
+          <t>AB Moving and Transportation LLC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>5121 N East River Rd Unit 2H
-Chicago IL 60656</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>contact@broadmiles.com</t>
+          <t>7127 Starmount Court,
+New Market, MD 21774</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>TRANZ AMERICA LLC</t>
+          <t>OSKAR EX INCORPORATED</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>4319 Chuck Hollow Ln, Apt #206
-Charlotte NC 28277</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>hr@tranzamericallc.com</t>
+          <t>9100 Trinity Dr,
+Lake in the Hills, IL 60156</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>GLOVBE GROUP INC</t>
+          <t>BKK LOGISTICS LLC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>9235 Trade Place Unit F
-San Diego, CA 92126</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>hr@eztransgroup.com</t>
+          <t>1405 COLUMBIA DR
+MIDLOTHIAN TX 76065</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MK TRANSPORTATION INC</t>
+          <t>TK Haul DBA A to Z Expeditors</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>1825 Bridgetown Pike Apt 510
-Feasterville-Trevose 19053</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr"/>
+          <t>115 E. Irving Park Rd.
+Streamwood, IL 60107</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">ABILOO LLC
-</t>
+          <t>MJ Transportations LLC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>96 BOLTON ST
-MARLBOROUGH, MA   01752</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>HR.ABILOOLLC@gmail.com</t>
+          <t>11132 S Towne Sq
+St. Louis. MO 63123</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>AVE-TRANS LLC</t>
+          <t>OLGAS TEAM CORP</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>6800 BERMUDA AVE
-MCKINNEY, TX 75070</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr"/>
+          <t>1111 W HINTZ RD
+ARLINGTON HEIGHTS, 60004</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sunnyland Express Corp</t>
+          <t>Off Max Logistics LLC</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>1336 Oleri Ter
-Fort Lee, NJ 07024</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr"/>
+          <t>1430 Bradley Lane Suite 102
+Carrollton, TX 75007</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>V&amp;T Express</t>
+          <t>Prime Line Logistics INC</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>113 Ashland Ter
-Boiling Springs, SC 29316</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>vtexpress@outlook.com</t>
+          <t>101 Trollingwood Way
+Pelzer, SC 29669</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>LANA EXPRESS LOGISTICS LLC</t>
+          <t>Total Quality Logistics</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>2807 ALLEN ST 2067
-DALLAS, TX 75204</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>operations@lanaexpressusa.com</t>
+          <t>4270 Ivy Pointe Blvd.
+Cincinnati, OH 45245</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Green Oaks Transportation LLC</t>
+          <t>Smart Way Logistics LLC</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>27425 Ferry Rd
-Warrenville, IL 60555</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr"/>
+          <t>8011 NORTH POINT BOULEVARD SUITE 102
+WINSTON SALEM, NC 27106</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Park Trans LLC</t>
+          <t>Black Sea Group LLC</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>711 Dolly Parton pkwy 4668
-Sevierville, TN 37862</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>hr@parktransllc.com</t>
+          <t>20800 Center Ridge Rd Ste 324
+Rocky River, OH 44116</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>DLH TRANS LLC</t>
+          <t>GO LOGISTIX INC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>292 S PINE ST
-SPARTANBURG, SC 29302</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>24328 VERMONT AVE STE 352
+HARBOR CITY, CA 90710</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>USA 1 TRUCKING LLC</t>
+          <t>TRANSGEORGIA LLC</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>5906 PARK AVE
-CLEVELEND, OH 44105</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>hr@usa1trucking.com</t>
+          <t>5540 PERRYTOWN DR
+W BLOOMFIELD, MI 48322</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">AB Moving and Transportation LLC
-</t>
+          <t>SKYFREIGHT INC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>7127 Starmount Court,
-New Market, MD 21774</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr"/>
+          <t>2 CLOVER
+IRVINE, CA 92604</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">OSKAR EX INCORPORATED
-</t>
+          <t>Highway App, Inc.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>9100 Trinity Dr,
-Lake in the Hills, IL 60156</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>5931 Greenville Ave, Unit #5620
+Dallas, TX 75206</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">BKK LOGISTICS LLC
-</t>
+          <t>Assure Assist</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>1405 COLUMBIA DR
-MIDLOTHIAN TX 76065</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Bkklmanagement@gmail.com</t>
+          <t>543 Country Club Dr,
+Simi Valley, CA 93065</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>TK Haul DBA A to Z Expeditors</t>
+          <t>NA Logistics, Inc</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>115 E. Irving Park Rd.
-Unit 789 
-Streamwood, IL 60107</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>hr@atozexpeditors.com</t>
+          <t>13208 CLUB HOUSE RD,
+PRESTO, PA 15142</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">MJ Transportations LLC
-</t>
+          <t>Novalogic LLC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>11132 S Towne Sq
-Suite 203 
-St. Louis. MO 63123</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Support@mjtransportations.com</t>
+          <t>2607 Woodruff Rd Ste E #3088
+Simpsonville, SC 29681</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OLGAS TEAM CORP</t>
+          <t>MAR BEE INC</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>1111 W HINTZ RD
-ARLINGTON HEIGHTS, 60004</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>hr@olgasteam.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Off Max Logistics LLC</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1430 Bradley Lane Suite 102   
-Carrollton, TX 75007 </t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>hrteam@offmaxlogisticsllc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Prime Line Logistics INC</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>101 Trollingwood Way
-Pelzer, SC 29669</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>hr@primelineservices.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Pennsylvania Logistics LLC</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>1631 Loretta Ave D
-Feasterville - Trevose, PA 19053</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Hr@pennlogisticsllc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Total Quality Logistics</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> 4270 Ivy Pointe Blvd.
-Cincinnati, OH 45245</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>riskmanagement@tql.com
-transportation@truckstop.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Smart Way Logistics LLC 
-</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8011 NORTH POINT BOULEVARD SUITE 102
-WINSTON SALEM, NC   27106  </t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Alexmorgan@smartwaylogisticsllc.com
-</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Black Sea Group LLC 
-</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>20800 Center Ridge Rd Ste 324
-Rocky River, OH 44116</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Operation@bsea.llc</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>GO LOGISTIX INC</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>24328 VERMONT AVE STE 352
-HARBOR CITY, CA 90710</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>sarah@gologistixinc.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TRANSGEORGIA LLC </t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5540 PERRYTOWN DR
-W BLOOMFIELD, MI   48322  </t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>recruiting@transgeorgia.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SKYFREIGHT INC </t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2 CLOVER
-IRVINE, CA   92604  </t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>dispatch@skyfreight.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Highway App, Inc.</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>5931 Greenville Ave, Unit #5620
-Dallas, TX 75206</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>insurance@certs.highway.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Assure Assist</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>543 Country Club Dr,
-Simi Valley, CA 93065</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>coi@assureassist.com</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Enterprise FM Trust</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>PO Box 16805,
-SAINT LOUIS, MO 63105</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr"/>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Wingstar Transportation LLC</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>480 E. Highland Rd,
-MACEDONIA, OH 44056</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Rise Logistics Corp</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>H11 East Garden Way,
-DAYTON, NJ 08810</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr"/>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Revolution Transport LLC</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>257 Main Street, 103,
-WADSWORTH, OH 44281</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr"/>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>RTS Financial</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>9300 Metcalf Ave,
-OVERLAND PARK, KS 66212</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>Veload Inc</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>1809 Jackson Street, 817,
-HOLLYWOOD, FL 33020</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>MAX CARGO LLC</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>8011 North Point Blvd, 102U2,
-WINSTON SALEM, NC 27106</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>USA Delivery Inc</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>7101 Virginia Pkwy, 1227,
-MCKINNEY, TX 75071</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Golden Eagle Transportation LLC</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>505 Lakeland Plaza Ste 386,
-CUMMING, GA 30040</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>HH Express Inc</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>6741 Ringgold Rd Suite C,
-CHATTANOOGA, TN 37412</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>Registry Monitoring Insurance Services Inc</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>2261 Market St. PMB 85402,
-SAN FRANCISCO, CA 94114</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Wonder Line Inc</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>6100 Oak Tree Blvd Ste 294,
-INDEPENDENCE, OH 44131</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>ArcBest II Inc and Affiliated Companies</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>8401 McClure Dr,
-FORT SMITH, AR 72916</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Descartes MyCarrierPortal</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>543 Country Club Dr Unit B338,
-SIMI VALLEY, CA 93065</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr"/>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Falcon Logistics Inc</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>2550 Five Star Pkwy Ste 136,
-BESSEMER, AL 35023</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr"/>
+          <t>102 HOMESTEAD RD.
+ANDERSON, SC 29621</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
